--- a/ET/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -1525,7 +1525,7 @@
         <v>99001</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ET/Unity/Assets/Config/Excel/MonsterConfig.xlsx
+++ b/ET/Unity/Assets/Config/Excel/MonsterConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
   <si>
     <t>cs</t>
   </si>
@@ -62,9 +62,18 @@
     <t>是否Boss(0/1)</t>
   </si>
   <si>
+    <t>技能ID列表</t>
+  </si>
+  <si>
     <t>碰撞半径</t>
   </si>
   <si>
+    <t>普攻</t>
+  </si>
+  <si>
+    <t>高度</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -96,6 +105,9 @@
   </si>
   <si>
     <t>AIconfigId</t>
+  </si>
+  <si>
+    <t>SkillIds</t>
   </si>
   <si>
     <r>
@@ -117,6 +129,12 @@
       </rPr>
       <t> </t>
     </r>
+  </si>
+  <si>
+    <t>BasicAttackSkillId</t>
+  </si>
+  <si>
+    <t>Height</t>
   </si>
   <si>
     <t>int</t>
@@ -843,7 +861,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -879,6 +897,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1227,7 +1248,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:P13"/>
+  <dimension ref="C1:Q13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="2" customWidth="1"/>
@@ -1239,12 +1260,12 @@
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="70" customWidth="1"/>
     <col min="11" max="12" width="12" customWidth="1"/>
-    <col min="13" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="12" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="13" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16">
+    <row r="1" spans="3:17">
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -1259,8 +1280,9 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
     </row>
-    <row r="2" spans="3:16">
+    <row r="2" spans="3:17">
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1294,11 +1316,12 @@
       <c r="M2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="3"/>
+      <c r="N2" s="2"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="3:16">
+    <row r="3" ht="24" customHeight="1" spans="3:17">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1332,107 +1355,128 @@
       <c r="M3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
+      <c r="O3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" ht="15.75" spans="3:16">
+    <row r="4" ht="25.5" spans="3:17">
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
+        <v>26</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="5" spans="3:16">
+    <row r="5" spans="3:17">
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="6" spans="3:16">
+    <row r="6" spans="3:17">
       <c r="C6" s="8">
         <v>2001</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H6" s="8">
         <v>1001</v>
@@ -1441,7 +1485,7 @@
         <v>100</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K6" s="8">
         <v>0</v>
@@ -1452,13 +1496,20 @@
       <c r="M6" s="9">
         <v>2001</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9">
+        <v>2001</v>
+      </c>
+      <c r="O6" s="10">
         <v>30</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="P6" s="10">
+        <v>200100</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="3:16">
+    <row r="7" spans="3:17">
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -1470,11 +1521,12 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="9"/>
-      <c r="N7" s="11"/>
+      <c r="N7" s="9"/>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
     </row>
-    <row r="8" spans="3:16">
+    <row r="8" spans="3:17">
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1489,22 +1541,23 @@
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
     </row>
-    <row r="13" spans="3:16">
+    <row r="13" spans="3:17">
       <c r="C13" s="8">
         <v>99001</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H13" s="8">
         <v>1001</v>
@@ -1513,7 +1566,7 @@
         <v>100</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="K13" s="8">
         <v>0</v>
@@ -1524,7 +1577,8 @@
       <c r="M13" s="9">
         <v>99001</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="13"/>
+      <c r="O13">
         <v>30</v>
       </c>
     </row>
